--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.00973617797613</v>
+        <v>3.089082128921121</v>
       </c>
       <c r="D2" t="n">
-        <v>18.53835209503529</v>
+        <v>3.012482215443235</v>
       </c>
       <c r="E2" t="n">
-        <v>3.04694574957441</v>
+        <v>0.4951286843058416</v>
       </c>
       <c r="F2" t="n">
-        <v>2.965698231614673</v>
+        <v>0.4819259626373844</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.91584467882731</v>
+        <v>2.098824760309438</v>
       </c>
       <c r="D3" t="n">
-        <v>12.60695563180594</v>
+        <v>2.048630290168466</v>
       </c>
       <c r="E3" t="n">
-        <v>3.04694574957441</v>
+        <v>0.4951286843058416</v>
       </c>
       <c r="F3" t="n">
-        <v>2.965698231614673</v>
+        <v>0.4819259626373844</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
